--- a/summary_report.xlsx
+++ b/summary_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>文件名称</t>
   </si>
@@ -41,22 +41,28 @@
     <t>寄样总支出（产品+物流）总和</t>
   </si>
   <si>
-    <t>All order-2025-12-07-02_42.csv</t>
-  </si>
-  <si>
-    <t>All order-2025-12-07-02_43.csv</t>
-  </si>
-  <si>
-    <t>06/12/2025</t>
-  </si>
-  <si>
-    <t>29/11/2025</t>
+    <t>All order-2025-12-15-03_22.csv</t>
+  </si>
+  <si>
+    <t>All order-2025-12-15-03_25.csv</t>
+  </si>
+  <si>
+    <t>14/12/2025</t>
+  </si>
+  <si>
+    <t>07/12/2025</t>
   </si>
   <si>
     <t>产品名称</t>
   </si>
   <si>
     <t>身体乳300ml单瓶</t>
+  </si>
+  <si>
+    <t>身体乳300ml双瓶</t>
+  </si>
+  <si>
+    <t>身体乳300ml三瓶</t>
   </si>
   <si>
     <t>身体乳单瓶</t>
@@ -466,22 +472,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>6620711</v>
+        <v>7939718</v>
       </c>
       <c r="D2">
-        <v>1839.09</v>
+        <v>2205.48</v>
       </c>
       <c r="E2">
-        <v>6214202</v>
+        <v>7229863</v>
       </c>
       <c r="F2">
-        <v>594.79</v>
+        <v>705.25</v>
       </c>
       <c r="G2">
-        <v>348.06</v>
+        <v>436.32</v>
       </c>
       <c r="H2">
-        <v>779.72</v>
+        <v>727.04</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -492,22 +498,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>5581749</v>
+        <v>6315826</v>
       </c>
       <c r="D3">
-        <v>1550.49</v>
+        <v>1754.4</v>
       </c>
       <c r="E3">
-        <v>5062263</v>
+        <v>5897917</v>
       </c>
       <c r="F3">
-        <v>562.46</v>
+        <v>561.1999999999999</v>
       </c>
       <c r="G3">
-        <v>332.04</v>
+        <v>328.31</v>
       </c>
       <c r="H3">
-        <v>465.96</v>
+        <v>779.72</v>
       </c>
     </row>
   </sheetData>
@@ -517,7 +523,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -536,10 +542,10 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -547,10 +553,10 @@
         <v>14</v>
       </c>
       <c r="B3">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -558,10 +564,10 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -569,10 +575,10 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -580,10 +586,10 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -591,10 +597,32 @@
         <v>18</v>
       </c>
       <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
         <v>2</v>
       </c>
-      <c r="C7">
-        <v>0</v>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/summary_report.xlsx
+++ b/summary_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>文件名称</t>
   </si>
@@ -41,43 +41,22 @@
     <t>寄样总支出（产品+物流）总和</t>
   </si>
   <si>
-    <t>All order-2025-12-15-03_22.csv</t>
-  </si>
-  <si>
-    <t>All order-2025-12-15-03_25.csv</t>
-  </si>
-  <si>
-    <t>14/12/2025</t>
-  </si>
-  <si>
-    <t>07/12/2025</t>
+    <t>全部_笔订单-2026-01-12-10_00.csv</t>
+  </si>
+  <si>
+    <t>11/01/2026</t>
   </si>
   <si>
     <t>产品名称</t>
   </si>
   <si>
-    <t>身体乳300ml单瓶</t>
-  </si>
-  <si>
-    <t>身体乳300ml双瓶</t>
-  </si>
-  <si>
-    <t>身体乳300ml三瓶</t>
-  </si>
-  <si>
-    <t>身体乳单瓶</t>
-  </si>
-  <si>
-    <t>身体乳双瓶</t>
-  </si>
-  <si>
-    <t>身体乳三瓶</t>
-  </si>
-  <si>
-    <t>防晒霜单瓶</t>
-  </si>
-  <si>
     <t>精华液单瓶</t>
+  </si>
+  <si>
+    <t>精华液双瓶</t>
+  </si>
+  <si>
+    <t>精华液三瓶</t>
   </si>
 </sst>
 </file>
@@ -435,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -469,51 +448,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>7939718</v>
+        <v>8636011</v>
       </c>
       <c r="D2">
-        <v>2205.48</v>
+        <v>2398.89</v>
       </c>
       <c r="E2">
-        <v>7229863</v>
+        <v>6648912</v>
       </c>
       <c r="F2">
-        <v>705.25</v>
+        <v>676.5</v>
       </c>
       <c r="G2">
-        <v>436.32</v>
+        <v>223.95</v>
       </c>
       <c r="H2">
-        <v>727.04</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>6315826</v>
-      </c>
-      <c r="D3">
-        <v>1754.4</v>
-      </c>
-      <c r="E3">
-        <v>5897917</v>
-      </c>
-      <c r="F3">
-        <v>561.1999999999999</v>
-      </c>
-      <c r="G3">
-        <v>328.31</v>
-      </c>
-      <c r="H3">
-        <v>779.72</v>
+        <v>262.73</v>
       </c>
     </row>
   </sheetData>
@@ -523,106 +476,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
+      <c r="B3">
+        <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2">
-        <v>72</v>
-      </c>
-      <c r="C2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>12</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5">
-        <v>23</v>
-      </c>
-      <c r="C5">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8">
         <v>1</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
